--- a/haptfluxdata.xlsx
+++ b/haptfluxdata.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://solisservices-my.sharepoint.com/personal/y_f_bats_uu_nl/Documents/Documents/PhD/FluxModel/Rebuttal PP/GitHub/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="8_{09975473-98C4-4B9D-BDA2-FD2F8C02A0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EA128F1-DD53-4401-A897-D798A5A0B6E2}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{09975473-98C4-4B9D-BDA2-FD2F8C02A0D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F348746-21E5-4E0F-AAF2-70D48F15A6AB}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1F99F3E4-FFA8-4426-A55C-EE14EA4173E6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1F99F3E4-FFA8-4426-A55C-EE14EA4173E6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Units" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="14">
   <si>
     <t>Species</t>
   </si>
@@ -69,6 +70,15 @@
   </si>
   <si>
     <t>doi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">co2 </t>
+  </si>
+  <si>
+    <t>unitless fraction</t>
+  </si>
+  <si>
+    <t>μatm (pCO2)</t>
   </si>
 </sst>
 </file>
@@ -78,7 +88,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +109,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -121,13 +137,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,4 +612,40 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B4781FE-86BF-4DC7-9135-C2566F4F9840}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>